--- a/Tesorio_Tasks_Report_Sep_2026.xlsx
+++ b/Tesorio_Tasks_Report_Sep_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tesorio Tasks Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Data (calc)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Open &amp; In Progress" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Slow Tasks Sep - 26 (&gt;2d)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tesorio Tasks Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data (calc)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open &amp; In Progress" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slow Tasks Sep - 26 (&gt;2d)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -115,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -171,9 +171,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -256,13 +253,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -286,7 +283,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -335,7 +332,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -350,9 +347,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1215,7 +1212,7 @@
         </is>
       </c>
       <c r="J2" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1223,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1238,17 +1235,21 @@
       <c r="E3" s="16" t="n">
         <v>46295.8473037904</v>
       </c>
-      <c r="F3" s="17" t="n"/>
-      <c r="G3" s="8" t="n"/>
-      <c r="H3" s="8" t="n"/>
+      <c r="F3" s="16" t="n">
+        <v>46297.89848548773</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>2.1</v>
+      </c>
       <c r="I3" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J3" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J3" s="17" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1279,7 +1280,7 @@
         </is>
       </c>
       <c r="J4" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1311,7 +1312,7 @@
         </is>
       </c>
       <c r="J5" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1322,7 +1323,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1334,17 +1335,21 @@
       <c r="E6" s="16" t="n">
         <v>46295.82999761874</v>
       </c>
-      <c r="F6" s="17" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
+      <c r="F6" s="16" t="n">
+        <v>46297.90066613108</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>2.1</v>
+      </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J6" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1354,7 +1359,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1370,17 +1375,21 @@
       <c r="E7" s="16" t="n">
         <v>46295.81715916161</v>
       </c>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="8" t="n"/>
+      <c r="F7" s="16" t="n">
+        <v>46296.9622578851</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>1.1</v>
+      </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J7" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J7" s="17" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -1415,7 +1424,7 @@
         </is>
       </c>
       <c r="J8" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1426,7 +1435,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1438,17 +1447,21 @@
       <c r="E9" s="16" t="n">
         <v>46295.53130173276</v>
       </c>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
+      <c r="F9" s="16" t="n">
+        <v>46297.90512939211</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>2.4</v>
+      </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J9" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1458,7 +1471,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1470,17 +1483,21 @@
       <c r="E10" s="16" t="n">
         <v>46295.41324218673</v>
       </c>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
+      <c r="F10" s="16" t="n">
+        <v>46297.90541278831</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>2.5</v>
+      </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J10" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J10" s="17" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1490,7 +1507,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1502,17 +1519,21 @@
       <c r="E11" s="16" t="n">
         <v>46295.41019463229</v>
       </c>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
+      <c r="F11" s="16" t="n">
+        <v>46297.63285132115</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>2.2</v>
+      </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J11" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J11" s="17" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1522,7 +1543,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1534,17 +1555,21 @@
       <c r="E12" s="16" t="n">
         <v>46295.41019301316</v>
       </c>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
+      <c r="F12" s="16" t="n">
+        <v>46297.90551869114</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>2.5</v>
+      </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J12" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J12" s="17" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1554,7 +1579,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1566,17 +1591,21 @@
       <c r="E13" s="16" t="n">
         <v>46295.40630179936</v>
       </c>
-      <c r="F13" s="17" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="8" t="n"/>
+      <c r="F13" s="16" t="n">
+        <v>46297.90591743176</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>2.5</v>
+      </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J13" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1586,7 +1615,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1598,17 +1627,21 @@
       <c r="E14" s="16" t="n">
         <v>46295.4028445344</v>
       </c>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
+      <c r="F14" s="16" t="n">
+        <v>46297.60930815991</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>2.2</v>
+      </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J14" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J14" s="17" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1618,7 +1651,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1630,17 +1663,21 @@
       <c r="E15" s="16" t="n">
         <v>46295.40284453199</v>
       </c>
-      <c r="F15" s="17" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
+      <c r="F15" s="16" t="n">
+        <v>46297.60873750909</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>2.2</v>
+      </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J15" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1650,7 +1687,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1662,17 +1699,21 @@
       <c r="E16" s="16" t="n">
         <v>46295.39588878456</v>
       </c>
-      <c r="F16" s="17" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
+      <c r="F16" s="16" t="n">
+        <v>46297.60818584973</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>2.2</v>
+      </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J16" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J16" s="17" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1682,7 +1723,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1694,17 +1735,21 @@
       <c r="E17" s="16" t="n">
         <v>46295.38546710258</v>
       </c>
-      <c r="F17" s="17" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
+      <c r="F17" s="16" t="n">
+        <v>46297.910989316</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>2.5</v>
+      </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J17" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J17" s="17" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1735,7 +1780,7 @@
         </is>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1746,7 +1791,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1758,17 +1803,21 @@
       <c r="E19" s="16" t="n">
         <v>46295.38200262133</v>
       </c>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
+      <c r="F19" s="16" t="n">
+        <v>46297.90685418666</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>2.5</v>
+      </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J19" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J19" s="17" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1778,7 +1827,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1790,17 +1839,21 @@
       <c r="E20" s="16" t="n">
         <v>46295.38200081119</v>
       </c>
-      <c r="F20" s="17" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
+      <c r="F20" s="16" t="n">
+        <v>46297.90720249945</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>2.5</v>
+      </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J20" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J20" s="17" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1810,7 +1863,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1822,17 +1875,21 @@
       <c r="E21" s="16" t="n">
         <v>46295.38200078165</v>
       </c>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
+      <c r="F21" s="16" t="n">
+        <v>46297.90749832824</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>2.5</v>
+      </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J21" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="J21" s="17" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1842,7 +1899,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1854,17 +1911,21 @@
       <c r="E22" s="16" t="n">
         <v>46294.94797569286</v>
       </c>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
+      <c r="F22" s="16" t="n">
+        <v>46297.90939245616</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J22" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J22" s="17" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1895,7 +1956,7 @@
         </is>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1946,7 +2007,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1962,17 +2023,21 @@
       <c r="E25" s="16" t="n">
         <v>46294.84351551093</v>
       </c>
-      <c r="F25" s="17" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
+      <c r="F25" s="16" t="n">
+        <v>46296.94401471949</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>2.1</v>
+      </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J25" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J25" s="17" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1982,7 +2047,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1994,17 +2059,21 @@
       <c r="E26" s="16" t="n">
         <v>46294.81601985007</v>
       </c>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
+      <c r="F26" s="16" t="n">
+        <v>46297.58423878847</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>2.8</v>
+      </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J26" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J26" s="17" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -2014,7 +2083,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2026,17 +2095,21 @@
       <c r="E27" s="16" t="n">
         <v>46294.81255310785</v>
       </c>
-      <c r="F27" s="17" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
+      <c r="F27" s="16" t="n">
+        <v>46297.605347919</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>2.8</v>
+      </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J27" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J27" s="17" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -2067,7 +2140,7 @@
         </is>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2078,7 +2151,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2094,17 +2167,21 @@
       <c r="E29" s="16" t="n">
         <v>46294.74763160559</v>
       </c>
-      <c r="F29" s="17" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
+      <c r="F29" s="16" t="n">
+        <v>46296.94055273847</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>2.2</v>
+      </c>
       <c r="I29" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J29" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J29" s="17" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -2114,7 +2191,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2126,17 +2203,21 @@
       <c r="E30" s="16" t="n">
         <v>46294.38277407402</v>
       </c>
-      <c r="F30" s="17" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
+      <c r="F30" s="16" t="n">
+        <v>46296.9383809041</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>2.6</v>
+      </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J30" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J30" s="17" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -2146,7 +2227,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2158,17 +2239,21 @@
       <c r="E31" s="16" t="n">
         <v>46294.37852374057</v>
       </c>
-      <c r="F31" s="17" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
+      <c r="F31" s="16" t="n">
+        <v>46296.93831081549</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>2.6</v>
+      </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J31" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J31" s="17" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -2199,7 +2284,7 @@
         </is>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2231,7 +2316,7 @@
         </is>
       </c>
       <c r="J33" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2299,7 +2384,7 @@
         </is>
       </c>
       <c r="J35" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -2310,7 +2395,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2322,17 +2407,21 @@
       <c r="E36" s="16" t="n">
         <v>46293.92366401341</v>
       </c>
-      <c r="F36" s="17" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
+      <c r="F36" s="16" t="n">
+        <v>46296.02503846225</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>2.1</v>
+      </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J36" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="J36" s="17" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -2378,7 +2467,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2394,17 +2483,21 @@
       <c r="E38" s="16" t="n">
         <v>46293.85422056212</v>
       </c>
-      <c r="F38" s="17" t="n"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
+      <c r="F38" s="16" t="n">
+        <v>46296.02491052666</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>2.2</v>
+      </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J38" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="J38" s="17" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2439,7 +2532,7 @@
         </is>
       </c>
       <c r="J39" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2471,7 +2564,7 @@
         </is>
       </c>
       <c r="J40" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2482,7 +2575,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2498,17 +2591,21 @@
       <c r="E41" s="16" t="n">
         <v>46293.74707007646</v>
       </c>
-      <c r="F41" s="17" t="n"/>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
+      <c r="F41" s="16" t="n">
+        <v>46296.02152286148</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>2.3</v>
+      </c>
       <c r="I41" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J41" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="J41" s="17" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -2518,7 +2615,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2530,17 +2627,21 @@
       <c r="E42" s="16" t="n">
         <v>46293.71879415549</v>
       </c>
-      <c r="F42" s="17" t="n"/>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
+      <c r="F42" s="16" t="n">
+        <v>46296.016445129</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>55.1</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>2.3</v>
+      </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J42" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="J42" s="17" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -2550,7 +2651,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2566,17 +2667,21 @@
       <c r="E43" s="16" t="n">
         <v>46293.66721556267</v>
       </c>
-      <c r="F43" s="17" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="8" t="n"/>
+      <c r="F43" s="16" t="n">
+        <v>46296.0160020991</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>2.3</v>
+      </c>
       <c r="I43" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J43" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="J43" s="17" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2586,7 +2691,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2602,17 +2707,21 @@
       <c r="E44" s="16" t="n">
         <v>46293.64244734746</v>
       </c>
-      <c r="F44" s="17" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
+      <c r="F44" s="16" t="n">
+        <v>46296.93780076596</v>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>3.3</v>
+      </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J44" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="J44" s="17" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -2662,7 +2771,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2678,17 +2787,21 @@
       <c r="E46" s="16" t="n">
         <v>46293.64028824646</v>
       </c>
-      <c r="F46" s="17" t="n"/>
-      <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="n"/>
+      <c r="F46" s="16" t="n">
+        <v>46296.01367762688</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>2.4</v>
+      </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J46" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="J46" s="17" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -2698,7 +2811,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2714,17 +2827,21 @@
       <c r="E47" s="16" t="n">
         <v>46293.63517083443</v>
       </c>
-      <c r="F47" s="17" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
+      <c r="F47" s="16" t="n">
+        <v>46296.01252588032</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>2.4</v>
+      </c>
       <c r="I47" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J47" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="J47" s="17" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -2734,7 +2851,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2750,17 +2867,21 @@
       <c r="E48" s="16" t="n">
         <v>46293.63176590435</v>
       </c>
-      <c r="F48" s="17" t="n"/>
-      <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="n"/>
+      <c r="F48" s="16" t="n">
+        <v>46296.01177945814</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>2.4</v>
+      </c>
       <c r="I48" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J48" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="J48" s="17" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -2770,7 +2891,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -2786,17 +2907,21 @@
       <c r="E49" s="16" t="n">
         <v>46293.63140334711</v>
       </c>
-      <c r="F49" s="17" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
+      <c r="F49" s="16" t="n">
+        <v>46296.01154921508</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>2.4</v>
+      </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J49" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="J49" s="17" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -2806,7 +2931,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -2822,17 +2947,21 @@
       <c r="E50" s="16" t="n">
         <v>46293.61862521308</v>
       </c>
-      <c r="F50" s="17" t="n"/>
-      <c r="G50" s="8" t="n"/>
-      <c r="H50" s="8" t="n"/>
+      <c r="F50" s="16" t="n">
+        <v>46296.00998812225</v>
+      </c>
+      <c r="G50" s="8" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>2.4</v>
+      </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J50" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="J50" s="17" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -2899,7 +3028,7 @@
         </is>
       </c>
       <c r="J52" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -3607,7 +3736,7 @@
         </is>
       </c>
       <c r="J70" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -3675,7 +3804,7 @@
         </is>
       </c>
       <c r="J72" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -3743,7 +3872,7 @@
         </is>
       </c>
       <c r="J74" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -3891,7 +4020,7 @@
         </is>
       </c>
       <c r="J78" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
@@ -3959,7 +4088,7 @@
         </is>
       </c>
       <c r="J80" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -4063,7 +4192,7 @@
         </is>
       </c>
       <c r="J83" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
@@ -4251,7 +4380,7 @@
         </is>
       </c>
       <c r="J88" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -4619,7 +4748,7 @@
         </is>
       </c>
       <c r="J98" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -5063,7 +5192,7 @@
         </is>
       </c>
       <c r="J110" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111">
@@ -5131,7 +5260,7 @@
         </is>
       </c>
       <c r="J112" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113">
@@ -5347,7 +5476,7 @@
         </is>
       </c>
       <c r="J118" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119">
@@ -5683,7 +5812,7 @@
         </is>
       </c>
       <c r="J127" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128">
@@ -5715,7 +5844,7 @@
         </is>
       </c>
       <c r="J128" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="129">
@@ -5751,7 +5880,7 @@
         </is>
       </c>
       <c r="J129" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="130">
@@ -5959,7 +6088,7 @@
         </is>
       </c>
       <c r="J135" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136">
@@ -6067,7 +6196,7 @@
         </is>
       </c>
       <c r="J138" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139">
@@ -6359,7 +6488,7 @@
         </is>
       </c>
       <c r="J146" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="147">
@@ -6471,7 +6600,7 @@
         </is>
       </c>
       <c r="J149" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="150">
@@ -6747,7 +6876,7 @@
         </is>
       </c>
       <c r="J156" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157">
@@ -6975,7 +7104,7 @@
         </is>
       </c>
       <c r="J162" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="163">
@@ -7047,7 +7176,7 @@
         </is>
       </c>
       <c r="J164" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="165">
@@ -7959,7 +8088,7 @@
         </is>
       </c>
       <c r="J187" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="188">
@@ -8151,7 +8280,7 @@
         </is>
       </c>
       <c r="J192" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="193">
@@ -8162,7 +8291,7 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>TO DO</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -8178,17 +8307,21 @@
       <c r="E193" s="16" t="n">
         <v>46284.00367331483</v>
       </c>
-      <c r="F193" s="17" t="n"/>
-      <c r="G193" s="8" t="n"/>
-      <c r="H193" s="8" t="n"/>
+      <c r="F193" s="16" t="n">
+        <v>46296.00277432978</v>
+      </c>
+      <c r="G193" s="8" t="n">
+        <v>288</v>
+      </c>
+      <c r="H193" s="8" t="n">
+        <v>12</v>
+      </c>
       <c r="I193" s="17" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="J193" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="J193" s="17" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -17103,7 +17236,7 @@
         </is>
       </c>
       <c r="J418" s="7" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="419">
@@ -17335,7 +17468,7 @@
         </is>
       </c>
       <c r="J424" s="7" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="425">
@@ -39235,7 +39368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -39310,7 +39443,7 @@
         <v>46160.70905254818</v>
       </c>
       <c r="F4" s="19" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5">
@@ -39338,13 +39471,13 @@
         <v>46163.55055680347</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>INV00028530</t>
+          <t>465954</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
@@ -39357,13 +39490,9 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Maryam Miner</t>
-        </is>
-      </c>
+      <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="16" t="n">
-        <v>46284.00367331483</v>
+        <v>46286.38041953123</v>
       </c>
       <c r="F6" s="19" t="n">
         <v>11</v>
@@ -39387,10 +39516,10 @@
       </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="16" t="n">
-        <v>46286.83348659906</v>
+        <v>46286.94855186724</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -39411,10 +39540,10 @@
       </c>
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="16" t="n">
-        <v>46286.94855186724</v>
+        <v>46286.83348659906</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -39435,16 +39564,16 @@
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="16" t="n">
-        <v>46286.38041953123</v>
+        <v>46287.8716530599</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>465954</t>
+          <t>INV00022389</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
@@ -39457,12 +39586,16 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Israel Illescas</t>
+        </is>
+      </c>
       <c r="E10" s="16" t="n">
-        <v>46287.8716530599</v>
+        <v>46287.69308431286</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -39483,16 +39616,16 @@
       </c>
       <c r="D11" s="3" t="inlineStr"/>
       <c r="E11" s="16" t="n">
-        <v>46287.93758657712</v>
+        <v>46287.40852433928</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>INV00022389</t>
+          <t>465954</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
@@ -39505,22 +39638,18 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Israel Illescas</t>
-        </is>
-      </c>
+      <c r="D12" s="3" t="inlineStr"/>
       <c r="E12" s="16" t="n">
-        <v>46287.69308431286</v>
+        <v>46287.93758657712</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>465954</t>
+          <t>471292</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
@@ -39533,12 +39662,16 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Raúl Pérez</t>
+        </is>
+      </c>
       <c r="E13" s="16" t="n">
-        <v>46287.40852433928</v>
+        <v>46288.9164218414</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -39559,16 +39692,16 @@
       </c>
       <c r="D14" s="3" t="inlineStr"/>
       <c r="E14" s="16" t="n">
-        <v>46288.9726488253</v>
+        <v>46288.37877095612</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>471292</t>
+          <t>465954</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
@@ -39581,16 +39714,12 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Raúl Pérez</t>
-        </is>
-      </c>
+      <c r="D15" s="3" t="inlineStr"/>
       <c r="E15" s="16" t="n">
-        <v>46288.9164218414</v>
+        <v>46288.9726488253</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -39614,7 +39743,7 @@
         <v>46288.8230048945</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -39635,10 +39764,10 @@
       </c>
       <c r="D17" s="3" t="inlineStr"/>
       <c r="E17" s="16" t="n">
-        <v>46288.37877095612</v>
+        <v>46289.9410656419</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -39659,10 +39788,10 @@
       </c>
       <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="16" t="n">
-        <v>46289.38261145303</v>
-      </c>
-      <c r="F18" s="20" t="n">
-        <v>6</v>
+        <v>46289.82310736993</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -39683,10 +39812,10 @@
       </c>
       <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="16" t="n">
-        <v>46289.9410656419</v>
-      </c>
-      <c r="F19" s="20" t="n">
-        <v>6</v>
+        <v>46289.38261145303</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -39707,10 +39836,10 @@
       </c>
       <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="16" t="n">
-        <v>46289.82310736993</v>
-      </c>
-      <c r="F20" s="20" t="n">
-        <v>6</v>
+        <v>46290.9549574777</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -39731,10 +39860,10 @@
       </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="16" t="n">
-        <v>46290.38750898977</v>
-      </c>
-      <c r="F21" s="20" t="n">
-        <v>5</v>
+        <v>46290.82651162384</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -39755,10 +39884,10 @@
       </c>
       <c r="D22" s="3" t="inlineStr"/>
       <c r="E22" s="16" t="n">
-        <v>46290.9549574777</v>
-      </c>
-      <c r="F22" s="20" t="n">
-        <v>5</v>
+        <v>46290.38750898977</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -39779,10 +39908,10 @@
       </c>
       <c r="D23" s="3" t="inlineStr"/>
       <c r="E23" s="16" t="n">
-        <v>46290.82651162384</v>
+        <v>46291.37707352559</v>
       </c>
       <c r="F23" s="20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -39803,10 +39932,10 @@
       </c>
       <c r="D24" s="3" t="inlineStr"/>
       <c r="E24" s="16" t="n">
-        <v>46291.79870046081</v>
+        <v>46291.9237020511</v>
       </c>
       <c r="F24" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -39827,10 +39956,10 @@
       </c>
       <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="16" t="n">
-        <v>46291.37707352559</v>
+        <v>46291.79870046081</v>
       </c>
       <c r="F25" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -39851,10 +39980,10 @@
       </c>
       <c r="D26" s="3" t="inlineStr"/>
       <c r="E26" s="16" t="n">
-        <v>46291.9237020511</v>
+        <v>46292.37349201113</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -39878,7 +40007,7 @@
         <v>46292.92369845757</v>
       </c>
       <c r="F27" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -39902,13 +40031,13 @@
         <v>46292.80217047067</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>465954</t>
+          <t>INV00026762</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
@@ -39918,21 +40047,25 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr"/>
+          <t>URGENT</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Fernanda Sánchez</t>
+        </is>
+      </c>
       <c r="E29" s="16" t="n">
-        <v>46292.37349201113</v>
+        <v>46293.83731812669</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>INV00028515</t>
+          <t>465954</t>
         </is>
       </c>
       <c r="B30" s="17" t="inlineStr">
@@ -39945,22 +40078,18 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Israel Illescas</t>
-        </is>
-      </c>
+      <c r="D30" s="3" t="inlineStr"/>
       <c r="E30" s="16" t="n">
-        <v>46293.63140334711</v>
+        <v>46293.94454117039</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>INV00029180</t>
+          <t>INV00029341</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
@@ -39973,16 +40102,12 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Israel Illescas</t>
-        </is>
-      </c>
+      <c r="D31" s="3" t="inlineStr"/>
       <c r="E31" s="16" t="n">
-        <v>46293.63176590435</v>
+        <v>46293.93060948811</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -40003,16 +40128,16 @@
       </c>
       <c r="D32" s="3" t="inlineStr"/>
       <c r="E32" s="16" t="n">
-        <v>46293.37199631524</v>
+        <v>46293.82308515597</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>INV00028251</t>
+          <t>465954</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
@@ -40025,16 +40150,12 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Israel Illescas</t>
-        </is>
-      </c>
+      <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="16" t="n">
-        <v>46293.61862521308</v>
+        <v>46293.37199631524</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -40055,16 +40176,16 @@
       </c>
       <c r="D34" s="3" t="inlineStr"/>
       <c r="E34" s="16" t="n">
-        <v>46293.94454117039</v>
+        <v>46294.80912935435</v>
       </c>
       <c r="F34" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>INV00029341</t>
+          <t>465954</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
@@ -40079,16 +40200,16 @@
       </c>
       <c r="D35" s="3" t="inlineStr"/>
       <c r="E35" s="16" t="n">
-        <v>46293.93060948811</v>
+        <v>46294.9341187737</v>
       </c>
       <c r="F35" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>465710</t>
+          <t>465954</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
@@ -40101,22 +40222,18 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Roberto Vázquez</t>
-        </is>
-      </c>
+      <c r="D36" s="3" t="inlineStr"/>
       <c r="E36" s="16" t="n">
-        <v>46293.66721556267</v>
+        <v>46294.37220843747</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>INV00020445</t>
+          <t>465954</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
@@ -40129,13 +40246,9 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Israel Illescas</t>
-        </is>
-      </c>
+      <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="16" t="n">
-        <v>46293.64244734746</v>
+        <v>46295.38261515521</v>
       </c>
       <c r="F37" s="20" t="n">
         <v>2</v>
@@ -40144,7 +40257,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>INV00029328</t>
+          <t>465954</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
@@ -40159,7 +40272,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr"/>
       <c r="E38" s="16" t="n">
-        <v>46293.92366401341</v>
+        <v>46295.9549493383</v>
       </c>
       <c r="F38" s="20" t="n">
         <v>2</v>
@@ -40168,7 +40281,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>INV00023441</t>
+          <t>INV00026301</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
@@ -40183,11 +40296,11 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Diana Escobar</t>
+          <t>Alberto Mirón 🦅</t>
         </is>
       </c>
       <c r="E39" s="16" t="n">
-        <v>46293.85422056212</v>
+        <v>46295.56925285065</v>
       </c>
       <c r="F39" s="20" t="n">
         <v>2</v>
@@ -40196,7 +40309,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>INV00029103</t>
+          <t>465954</t>
         </is>
       </c>
       <c r="B40" s="17" t="inlineStr">
@@ -40209,13 +40322,9 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Fernanda Sánchez</t>
-        </is>
-      </c>
+      <c r="D40" s="3" t="inlineStr"/>
       <c r="E40" s="16" t="n">
-        <v>46293.74707007646</v>
+        <v>46295.83003620177</v>
       </c>
       <c r="F40" s="20" t="n">
         <v>2</v>
@@ -40224,7 +40333,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>442515</t>
+          <t>INV00029689</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
@@ -40239,854 +40348,10 @@
       </c>
       <c r="D41" s="3" t="inlineStr"/>
       <c r="E41" s="16" t="n">
-        <v>46293.71879415549</v>
+        <v>46295.83345593969</v>
       </c>
       <c r="F41" s="20" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>INV00026762</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>URGENT</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Fernanda Sánchez</t>
-        </is>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>46293.83731812669</v>
-      </c>
-      <c r="F42" s="20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>465954</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="16" t="n">
-        <v>46293.82308515597</v>
-      </c>
-      <c r="F43" s="20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>INV00029156</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Israel Illescas</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>46293.64028824646</v>
-      </c>
-      <c r="F44" s="20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>INV00029028</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Israel Illescas</t>
-        </is>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>46293.63517083443</v>
-      </c>
-      <c r="F45" s="20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>INV00029477</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="16" t="n">
-        <v>46294.81255310785</v>
-      </c>
-      <c r="F46" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>465954</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="16" t="n">
-        <v>46294.80912935435</v>
-      </c>
-      <c r="F47" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>465954</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="16" t="n">
-        <v>46294.9341187737</v>
-      </c>
-      <c r="F48" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>INV00029564</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="16" t="n">
-        <v>46294.94797569286</v>
-      </c>
-      <c r="F49" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>INV00029393</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="16" t="n">
-        <v>46294.37852374057</v>
-      </c>
-      <c r="F50" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>465954</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="16" t="n">
-        <v>46294.37220843747</v>
-      </c>
-      <c r="F51" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>450391</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr"/>
-      <c r="E52" s="16" t="n">
-        <v>46294.38277407402</v>
-      </c>
-      <c r="F52" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>468460</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Paolet Ordóñez</t>
-        </is>
-      </c>
-      <c r="E53" s="16" t="n">
-        <v>46294.74763160559</v>
-      </c>
-      <c r="F53" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>INV00029452</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="16" t="n">
-        <v>46294.81601985007</v>
-      </c>
-      <c r="F54" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>464959</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Roberto Vázquez</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>46294.84351551093</v>
-      </c>
-      <c r="F55" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>465954</t>
-        </is>
-      </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="16" t="n">
-        <v>46295.83003620177</v>
-      </c>
-      <c r="F56" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>INV00029689</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="16" t="n">
-        <v>46295.83345593969</v>
-      </c>
-      <c r="F57" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>INV00029767</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="16" t="n">
-        <v>46295.8473037904</v>
-      </c>
-      <c r="F58" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>465954</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="16" t="n">
-        <v>46295.9549493383</v>
-      </c>
-      <c r="F59" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>INV00027255</t>
-        </is>
-      </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr"/>
-      <c r="E60" s="16" t="n">
-        <v>46295.53130173276</v>
-      </c>
-      <c r="F60" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>INV00026301</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Alberto Mirón 🦅</t>
-        </is>
-      </c>
-      <c r="E61" s="16" t="n">
-        <v>46295.56925285065</v>
-      </c>
-      <c r="F61" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>468925</t>
-        </is>
-      </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Roberto Vázquez</t>
-        </is>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>46295.81715916161</v>
-      </c>
-      <c r="F62" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>INV00029687</t>
-        </is>
-      </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="16" t="n">
-        <v>46295.82999761874</v>
-      </c>
-      <c r="F63" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>INV00029676</t>
-        </is>
-      </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr"/>
-      <c r="E64" s="16" t="n">
-        <v>46295.38546710258</v>
-      </c>
-      <c r="F64" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>INV00029608</t>
-        </is>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr"/>
-      <c r="E65" s="16" t="n">
-        <v>46295.39588878456</v>
-      </c>
-      <c r="F65" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>INV00029628</t>
-        </is>
-      </c>
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr"/>
-      <c r="E66" s="16" t="n">
-        <v>46295.40284453199</v>
-      </c>
-      <c r="F66" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>INV00029625</t>
-        </is>
-      </c>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="16" t="n">
-        <v>46295.4028445344</v>
-      </c>
-      <c r="F67" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>INV00029657</t>
-        </is>
-      </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="16" t="n">
-        <v>46295.38200078165</v>
-      </c>
-      <c r="F68" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>INV00029659</t>
-        </is>
-      </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr"/>
-      <c r="E69" s="16" t="n">
-        <v>46295.38200081119</v>
-      </c>
-      <c r="F69" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>INV00029658</t>
-        </is>
-      </c>
-      <c r="B70" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr"/>
-      <c r="E70" s="16" t="n">
-        <v>46295.38200262133</v>
-      </c>
-      <c r="F70" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>465954</t>
-        </is>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="16" t="n">
-        <v>46295.38261515521</v>
-      </c>
-      <c r="F71" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>INV00029650</t>
-        </is>
-      </c>
-      <c r="B72" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr"/>
-      <c r="E72" s="16" t="n">
-        <v>46295.41324218673</v>
-      </c>
-      <c r="F72" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>INV00029641</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr"/>
-      <c r="E73" s="16" t="n">
-        <v>46295.41019463229</v>
-      </c>
-      <c r="F73" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>INV00029637</t>
-        </is>
-      </c>
-      <c r="B74" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr"/>
-      <c r="E74" s="16" t="n">
-        <v>46295.41019301316</v>
-      </c>
-      <c r="F74" s="21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>INV00029635</t>
-        </is>
-      </c>
-      <c r="B75" s="17" t="inlineStr">
-        <is>
-          <t>TO DO</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="16" t="n">
-        <v>46295.40630179936</v>
-      </c>
-      <c r="F75" s="21" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -41100,7 +40365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -41172,7 +40437,7 @@
       <c r="E4" s="16" t="n">
         <v>46295.14238037631</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="21">
         <f>(E4-D4)</f>
         <v/>
       </c>
@@ -41180,7 +40445,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>471856</t>
+          <t>INV00028530</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
@@ -41190,16 +40455,16 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Efraín Córdova</t>
+          <t>Maryam Miner</t>
         </is>
       </c>
       <c r="D5" s="16" t="n">
-        <v>46272.69119831221</v>
+        <v>46284.00367331483</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>46284.08243005152</v>
-      </c>
-      <c r="F5" s="22">
+        <v>46296.00277432978</v>
+      </c>
+      <c r="F5" s="21">
         <f>(E5-D5)</f>
         <v/>
       </c>
@@ -41207,7 +40472,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>INV00026486</t>
+          <t>471856</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
@@ -41217,16 +40482,16 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Roberto Vázquez</t>
+          <t>Efraín Córdova</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>46289.73804375815</v>
+        <v>46272.69119831221</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>46295.06242924267</v>
-      </c>
-      <c r="F6" s="22">
+        <v>46284.08243005152</v>
+      </c>
+      <c r="F6" s="21">
         <f>(E6-D6)</f>
         <v/>
       </c>
@@ -41234,7 +40499,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>INV00027967</t>
+          <t>INV00026486</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -41244,16 +40509,16 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Israel Illescas</t>
+          <t>Roberto Vázquez</t>
         </is>
       </c>
       <c r="D7" s="16" t="n">
-        <v>46286.84804495043</v>
+        <v>46289.73804375815</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>46291.00458753425</v>
-      </c>
-      <c r="F7" s="22">
+        <v>46295.06242924267</v>
+      </c>
+      <c r="F7" s="21">
         <f>(E7-D7)</f>
         <v/>
       </c>
@@ -41261,7 +40526,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>INV00029208</t>
+          <t>INV00027967</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
@@ -41269,14 +40534,18 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Israel Illescas</t>
+        </is>
+      </c>
       <c r="D8" s="16" t="n">
-        <v>46291.37852208241</v>
+        <v>46286.84804495043</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>46294.05232310918</v>
-      </c>
-      <c r="F8" s="22">
+        <v>46291.00458753425</v>
+      </c>
+      <c r="F8" s="21">
         <f>(E8-D8)</f>
         <v/>
       </c>
@@ -41284,7 +40553,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>450391</t>
+          <t>INV00020445</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
@@ -41292,14 +40561,18 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Israel Illescas</t>
+        </is>
+      </c>
       <c r="D9" s="16" t="n">
-        <v>46291.43832897197</v>
+        <v>46293.64244734746</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>46293.95908317615</v>
-      </c>
-      <c r="F9" s="22">
+        <v>46296.93780076596</v>
+      </c>
+      <c r="F9" s="21">
         <f>(E9-D9)</f>
         <v/>
       </c>
@@ -41307,7 +40580,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>INV00020003</t>
+          <t>INV00029564</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
@@ -41315,18 +40588,14 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Eduardo Paredes</t>
-        </is>
-      </c>
+      <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="16" t="n">
-        <v>46280.87289538589</v>
+        <v>46294.94797569286</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>46283.00781152549</v>
-      </c>
-      <c r="F10" s="22">
+        <v>46297.90939245616</v>
+      </c>
+      <c r="F10" s="21">
         <f>(E10-D10)</f>
         <v/>
       </c>
@@ -41334,7 +40603,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>450391</t>
+          <t>INV00029477</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
@@ -41344,12 +40613,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="16" t="n">
-        <v>46291.86163915828</v>
+        <v>46294.81255310785</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>46293.95906270872</v>
-      </c>
-      <c r="F11" s="22">
+        <v>46297.605347919</v>
+      </c>
+      <c r="F11" s="21">
         <f>(E11-D11)</f>
         <v/>
       </c>
@@ -41357,7 +40626,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>450391</t>
+          <t>INV00029452</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
@@ -41367,13 +40636,816 @@
       </c>
       <c r="C12" s="3" t="inlineStr"/>
       <c r="D12" s="16" t="n">
+        <v>46294.81601985007</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>46297.58423878847</v>
+      </c>
+      <c r="F12" s="21">
+        <f>(E12-D12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>INV00029208</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="16" t="n">
+        <v>46291.37852208241</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>46294.05232310918</v>
+      </c>
+      <c r="F13" s="21">
+        <f>(E13-D13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>INV00029393</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="16" t="n">
+        <v>46294.37852374057</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>46296.93831081549</v>
+      </c>
+      <c r="F14" s="21">
+        <f>(E14-D14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>450391</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="16" t="n">
+        <v>46294.38277407402</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>46296.9383809041</v>
+      </c>
+      <c r="F15" s="21">
+        <f>(E15-D15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>INV00029676</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="16" t="n">
+        <v>46295.38546710258</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>46297.910989316</v>
+      </c>
+      <c r="F16" s="21">
+        <f>(E16-D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>INV00029657</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="16" t="n">
+        <v>46295.38200078165</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>46297.90749832824</v>
+      </c>
+      <c r="F17" s="21">
+        <f>(E17-D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>INV00029659</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="16" t="n">
+        <v>46295.38200081119</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>46297.90720249945</v>
+      </c>
+      <c r="F18" s="21">
+        <f>(E18-D18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>INV00029658</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="16" t="n">
+        <v>46295.38200262133</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>46297.90685418666</v>
+      </c>
+      <c r="F19" s="21">
+        <f>(E19-D19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>450391</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="16" t="n">
+        <v>46291.43832897197</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>46293.95908317615</v>
+      </c>
+      <c r="F20" s="21">
+        <f>(E20-D20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>INV00029635</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="16" t="n">
+        <v>46295.40630179936</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>46297.90591743176</v>
+      </c>
+      <c r="F21" s="21">
+        <f>(E21-D21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>INV00029637</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="16" t="n">
+        <v>46295.41019301316</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>46297.90551869114</v>
+      </c>
+      <c r="F22" s="21">
+        <f>(E22-D22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>INV00029650</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="16" t="n">
+        <v>46295.41324218673</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>46297.90541278831</v>
+      </c>
+      <c r="F23" s="21">
+        <f>(E23-D23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>INV00028251</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Israel Illescas</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>46293.61862521308</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>46296.00998812225</v>
+      </c>
+      <c r="F24" s="21">
+        <f>(E24-D24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>INV00028515</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Israel Illescas</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>46293.63140334711</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>46296.01154921508</v>
+      </c>
+      <c r="F25" s="21">
+        <f>(E25-D25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>INV00029180</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Israel Illescas</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>46293.63176590435</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>46296.01177945814</v>
+      </c>
+      <c r="F26" s="21">
+        <f>(E26-D26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>INV00029028</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Israel Illescas</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>46293.63517083443</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>46296.01252588032</v>
+      </c>
+      <c r="F27" s="21">
+        <f>(E27-D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>INV00027255</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="16" t="n">
+        <v>46295.53130173276</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>46297.90512939211</v>
+      </c>
+      <c r="F28" s="21">
+        <f>(E28-D28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>INV00029156</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Israel Illescas</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>46293.64028824646</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>46296.01367762688</v>
+      </c>
+      <c r="F29" s="21">
+        <f>(E29-D29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>465710</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Roberto Vázquez</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>46293.66721556267</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>46296.0160020991</v>
+      </c>
+      <c r="F30" s="21">
+        <f>(E30-D30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>442515</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="16" t="n">
+        <v>46293.71879415549</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>46296.016445129</v>
+      </c>
+      <c r="F31" s="21">
+        <f>(E31-D31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>INV00029103</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Fernanda Sánchez</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>46293.74707007646</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>46296.02152286148</v>
+      </c>
+      <c r="F32" s="21">
+        <f>(E32-D32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>INV00029641</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="16" t="n">
+        <v>46295.41019463229</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>46297.63285132115</v>
+      </c>
+      <c r="F33" s="21">
+        <f>(E33-D33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>INV00029608</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="16" t="n">
+        <v>46295.39588878456</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>46297.60818584973</v>
+      </c>
+      <c r="F34" s="21">
+        <f>(E34-D34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>INV00029625</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="16" t="n">
+        <v>46295.4028445344</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>46297.60930815991</v>
+      </c>
+      <c r="F35" s="21">
+        <f>(E35-D35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>INV00029628</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="16" t="n">
+        <v>46295.40284453199</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>46297.60873750909</v>
+      </c>
+      <c r="F36" s="21">
+        <f>(E36-D36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>468460</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Paolet Ordóñez</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>46294.74763160559</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>46296.94055273847</v>
+      </c>
+      <c r="F37" s="21">
+        <f>(E37-D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>INV00023441</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Diana Escobar</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>46293.85422056212</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>46296.02491052666</v>
+      </c>
+      <c r="F38" s="21">
+        <f>(E38-D38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>INV00020003</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Eduardo Paredes</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>46280.87289538589</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>46283.00781152549</v>
+      </c>
+      <c r="F39" s="21">
+        <f>(E39-D39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>INV00029328</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr"/>
+      <c r="D40" s="16" t="n">
+        <v>46293.92366401341</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>46296.02503846225</v>
+      </c>
+      <c r="F40" s="21">
+        <f>(E40-D40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>464959</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Roberto Vázquez</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>46294.84351551093</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>46296.94401471949</v>
+      </c>
+      <c r="F41" s="21">
+        <f>(E41-D41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>450391</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="16" t="n">
+        <v>46291.86163915828</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>46293.95906270872</v>
+      </c>
+      <c r="F42" s="21">
+        <f>(E42-D42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>INV00029687</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="16" t="n">
+        <v>46295.82999761874</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>46297.90066613108</v>
+      </c>
+      <c r="F43" s="21">
+        <f>(E43-D43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>INV00029767</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="16" t="n">
+        <v>46295.8473037904</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>46297.89848548773</v>
+      </c>
+      <c r="F44" s="21">
+        <f>(E44-D44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>450391</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="16" t="n">
         <v>46291.9345038863</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E45" s="16" t="n">
         <v>46293.95904562659</v>
       </c>
-      <c r="F12" s="22">
-        <f>(E12-D12)</f>
+      <c r="F45" s="21">
+        <f>(E45-D45)</f>
         <v/>
       </c>
     </row>
